--- a/picxify/packages/sample-data/complex/ar_aging_snapshot.xlsx
+++ b/picxify/packages/sample-data/complex/ar_aging_snapshot.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,20 +444,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>61-90 Days</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Prepayments</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Credits</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Total AR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Source Modified</t>
         </is>
@@ -486,15 +491,18 @@
         <v>5661.77</v>
       </c>
       <c r="F2" t="n">
-        <v>25476.05</v>
+        <v>6793.61</v>
       </c>
       <c r="G2" t="n">
-        <v>17392.02</v>
+        <v>26088.03</v>
       </c>
       <c r="H2" t="n">
-        <v>9366.42</v>
-      </c>
-      <c r="I2" t="inlineStr">
+        <v>1027.39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>79226.09</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
@@ -517,21 +525,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35183.43</v>
+        <v>39262.98</v>
       </c>
       <c r="E3" t="n">
-        <v>14709.07</v>
+        <v>12003.85</v>
       </c>
       <c r="F3" t="n">
-        <v>24007.71</v>
+        <v>1625.14</v>
       </c>
       <c r="G3" t="n">
-        <v>4062.85</v>
+        <v>7515.48</v>
       </c>
       <c r="H3" t="n">
-        <v>26293.87</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>4263.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>46810.74</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
@@ -554,21 +565,24 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10101.03</v>
+        <v>34854.19</v>
       </c>
       <c r="E4" t="n">
-        <v>7378.37</v>
+        <v>7296.72</v>
       </c>
       <c r="F4" t="n">
-        <v>25937.52</v>
+        <v>5721.05</v>
       </c>
       <c r="G4" t="n">
-        <v>9728.959999999999</v>
+        <v>8060.05</v>
       </c>
       <c r="H4" t="n">
-        <v>65786.2</v>
-      </c>
-      <c r="I4" t="inlineStr">
+        <v>14720</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8668.26</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -591,21 +605,24 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12209.39</v>
+        <v>32095.39</v>
       </c>
       <c r="E5" t="n">
-        <v>11040</v>
+        <v>35.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1294.68</v>
+        <v>4805.28</v>
       </c>
       <c r="G5" t="n">
-        <v>15839.68</v>
+        <v>15802.96</v>
       </c>
       <c r="H5" t="n">
-        <v>5202.32</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>15012.14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20595.5</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
@@ -628,21 +645,24 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24825.1</v>
+        <v>30345.93</v>
       </c>
       <c r="E6" t="n">
-        <v>7901.48</v>
+        <v>4043.3</v>
       </c>
       <c r="F6" t="n">
-        <v>22518.21</v>
+        <v>7201.45</v>
       </c>
       <c r="G6" t="n">
-        <v>3669.53</v>
+        <v>507.04</v>
       </c>
       <c r="H6" t="n">
-        <v>68405.37</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>14881.39</v>
+      </c>
+      <c r="I6" t="n">
+        <v>74432.55</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
@@ -665,21 +685,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12243.03</v>
+        <v>35624.62</v>
       </c>
       <c r="E7" t="n">
-        <v>13502.72</v>
+        <v>5204.24</v>
       </c>
       <c r="F7" t="n">
-        <v>507.04</v>
+        <v>7510.78</v>
       </c>
       <c r="G7" t="n">
-        <v>14881.39</v>
+        <v>19948.49</v>
       </c>
       <c r="H7" t="n">
-        <v>74432.55</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>17923.37</v>
+      </c>
+      <c r="I7" t="n">
+        <v>82379.74000000001</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
@@ -702,21 +725,24 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35624.62</v>
+        <v>13225.2</v>
       </c>
       <c r="E8" t="n">
-        <v>5204.24</v>
+        <v>113.93</v>
       </c>
       <c r="F8" t="n">
-        <v>28165.43</v>
+        <v>2808.48</v>
       </c>
       <c r="G8" t="n">
-        <v>13298.99</v>
+        <v>20335.98</v>
       </c>
       <c r="H8" t="n">
-        <v>81174.3</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>13729.51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>82093.73</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -739,21 +765,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36593.3</v>
+        <v>24762.87</v>
       </c>
       <c r="E9" t="n">
-        <v>4431</v>
+        <v>14346.4</v>
       </c>
       <c r="F9" t="n">
-        <v>227.86</v>
+        <v>7505.46</v>
       </c>
       <c r="G9" t="n">
-        <v>7021.2</v>
+        <v>14721.04</v>
       </c>
       <c r="H9" t="n">
-        <v>62618.61</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>17761.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>77156.27</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
@@ -776,21 +805,24 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28086.06</v>
+        <v>31769.4</v>
       </c>
       <c r="E10" t="n">
-        <v>13604.78</v>
+        <v>14569.01</v>
       </c>
       <c r="F10" t="n">
-        <v>17970.68</v>
+        <v>6336.85</v>
       </c>
       <c r="G10" t="n">
-        <v>19128.53</v>
+        <v>19511.37</v>
       </c>
       <c r="H10" t="n">
-        <v>84745.56</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>7190.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>81651.31</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
@@ -813,21 +845,24 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20646.66</v>
+        <v>8449.76</v>
       </c>
       <c r="E11" t="n">
-        <v>13321.27</v>
+        <v>8638.969999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>25466.92</v>
+        <v>249.89</v>
       </c>
       <c r="G11" t="n">
-        <v>15668.1</v>
+        <v>14818.1</v>
       </c>
       <c r="H11" t="n">
-        <v>87557.7</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>14788.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24029.09</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
